--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486377_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486377_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.110900000000001</v>
+        <v>7.8913</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1003</v>
+        <v>5.4356</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0105</v>
+        <v>2.4557</v>
       </c>
       <c r="G2" t="n">
         <v>3.9706</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7705</v>
+        <v>0.551</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.536</v>
+        <v>-0.2007</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3065</v>
+        <v>0.7516</v>
       </c>
       <c r="V2" t="n">
         <v>2.0647</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3891</v>
+        <v>3.8517</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6301</v>
+        <v>3.1151</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7589</v>
+        <v>0.7367</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1453</v>
+        <v>1.9029</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8402</v>
+        <v>0.6813</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6948</v>
+        <v>1.2216</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2192</v>
+        <v>2.9231</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4869</v>
+        <v>1.448</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2677</v>
+        <v>1.475</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07389999999999999</v>
+        <v>-1.0202</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3532</v>
+        <v>-0.7668</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4271</v>
+        <v>-0.2534</v>
       </c>
       <c r="P3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.9576</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.435</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.3926</v>
-      </c>
       <c r="S3" t="n">
-        <v>0.3169</v>
+        <v>-0.4209</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8292</v>
+        <v>-0.0457</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5123</v>
+        <v>-0.3752</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2599</v>
+        <v>1.4997</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4552</v>
+        <v>1.3252</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1952</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8237</v>
+        <v>3.4931</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4878</v>
+        <v>1.5184</v>
       </c>
       <c r="F4" t="n">
-        <v>0.336</v>
+        <v>1.9747</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9029</v>
+        <v>-1.1453</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6813</v>
+        <v>-1.8402</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2216</v>
+        <v>0.6948</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9231</v>
+        <v>-1.2192</v>
       </c>
       <c r="K4" t="n">
-        <v>1.448</v>
+        <v>-1.4869</v>
       </c>
       <c r="L4" t="n">
-        <v>1.475</v>
+        <v>0.2677</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0202</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7668</v>
+        <v>-0.3532</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2534</v>
+        <v>0.4271</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4489</v>
+        <v>0.4209</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.7174</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7759</v>
+        <v>-0.2965</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4997</v>
+        <v>2.2599</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>2.4552</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1745</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2412</v>
+        <v>1.727</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1228</v>
+        <v>1.7223</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8816000000000001</v>
+        <v>0.0047</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9615</v>
+        <v>3.31</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7822</v>
+        <v>1.8246</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1793</v>
+        <v>1.4854</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8484</v>
+        <v>3.6138</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7337</v>
+        <v>2.0439</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1147</v>
+        <v>1.5698</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1131</v>
+        <v>-0.3038</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0486</v>
+        <v>-0.2193</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0645</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R5" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0621</v>
+        <v>0.0916</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1667</v>
+        <v>0.5011</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1046</v>
+        <v>-0.4095</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>-0.152</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3252</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5929</v>
+        <v>1.5998</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9838</v>
+        <v>1.0523</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6091</v>
+        <v>0.5475</v>
       </c>
       <c r="G6" t="n">
         <v>2.058</v>
@@ -922,13 +922,13 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0531</v>
+        <v>-0.0463</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0649</v>
+        <v>0.0036</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0118</v>
+        <v>-0.0499</v>
       </c>
       <c r="V6" t="n">
         <v>-1.282</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4658</v>
+        <v>1.0118</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4303</v>
+        <v>1.8934</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0356</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>3.31</v>
+        <v>1.9615</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8246</v>
+        <v>1.7822</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4854</v>
+        <v>0.1793</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6138</v>
+        <v>1.8484</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0439</v>
+        <v>1.7337</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5698</v>
+        <v>0.1147</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3038</v>
+        <v>0.1131</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2193</v>
+        <v>0.0486</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.0645</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5225</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1696</v>
+        <v>0.8328</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2091</v>
+        <v>0.9373</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3787</v>
+        <v>-0.1046</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.152</v>
+        <v>-1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.152</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0279</v>
+        <v>-0.1512</v>
       </c>
       <c r="E8" t="n">
         <v>0.2417</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2697</v>
+        <v>-0.393</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1392</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1062</v>
+        <v>-0.2295</v>
       </c>
       <c r="T8" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0377</v>
+        <v>-0.161</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3135</v>
+        <v>-0.6179</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7982</v>
+        <v>-1.1334</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4847</v>
+        <v>0.5155</v>
       </c>
       <c r="G9" t="n">
         <v>0.524</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4676</v>
+        <v>0.1631</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3341</v>
+        <v>-0.0012</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1335</v>
+        <v>0.1643</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.205</v>
+        <v>-1.9631</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3519</v>
+        <v>-3.1717</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1469</v>
+        <v>1.2085</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0871</v>
@@ -1234,13 +1234,13 @@
         <v>2.3926</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5309</v>
+        <v>-0.289</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3268</v>
+        <v>-0.1466</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2041</v>
+        <v>-0.1424</v>
       </c>
       <c r="V10" t="n">
         <v>-0.152</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>T. MCFADDEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8561</v>
+        <v>-2.6898</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0001</v>
+        <v>-2.8852</v>
       </c>
       <c r="F11" t="n">
-        <v>0.144</v>
+        <v>0.1954</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.536</v>
+        <v>-1.3467</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8643</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3283</v>
+        <v>-0.3976</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2841</v>
+        <v>-0.7935</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3989</v>
+        <v>-0.0333</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1147</v>
+        <v>-0.7601</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2519</v>
+        <v>-0.5532</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4654</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2136</v>
+        <v>0.3626</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.87</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.305</v>
+        <v>-3.9151</v>
       </c>
       <c r="R11" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.298</v>
+        <v>0.289</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.411</v>
+        <v>0.6934</v>
       </c>
       <c r="U11" t="n">
-        <v>0.113</v>
+        <v>-0.4044</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.152</v>
+        <v>0.9779</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>-0.152</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0377</v>
+        <v>-2.7443</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0302</v>
+        <v>-2.8884</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0074</v>
+        <v>0.144</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5602</v>
+        <v>-1.536</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.216</v>
+        <v>-1.8643</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3442</v>
+        <v>0.3283</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0382</v>
+        <v>-1.2841</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-1.3989</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0382</v>
+        <v>0.1147</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5985</v>
+        <v>-0.2519</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.216</v>
+        <v>-0.4654</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3825</v>
+        <v>0.2136</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2175</v>
+        <v>-0.1863</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.2992</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.149</v>
+        <v>0.113</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.2599</v>
+        <v>-0.152</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2599</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. MCFADDEN</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0868</v>
+        <v>-2.9692</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2205</v>
+        <v>0.0382</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1337</v>
+        <v>-3.0074</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3467</v>
+        <v>-0.5602</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.216</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3976</v>
+        <v>-0.3442</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7935</v>
+        <v>0.0382</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0333</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7601</v>
+        <v>0.0382</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5532</v>
+        <v>-0.5985</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.216</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3626</v>
+        <v>-0.3825</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.6101</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9151</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1079</v>
+        <v>-0.149</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3581</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.466</v>
+        <v>-0.149</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9779</v>
+        <v>-2.2599</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.152</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="14">
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.096600000000006</v>
+        <v>8.4392</v>
       </c>
       <c r="E14" t="n">
-        <v>4.595899999999999</v>
+        <v>4.9383</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5007</v>
+        <v>3.500700000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>7.912500000000001</v>
+        <v>7.9125</v>
       </c>
       <c r="H14" t="n">
         <v>0.4855999999999996</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4268</v>
+        <v>7.426799999999999</v>
       </c>
       <c r="J14" t="n">
         <v>11.7947</v>
@@ -1525,7 +1525,7 @@
         <v>5.6587</v>
       </c>
       <c r="L14" t="n">
-        <v>6.135899999999999</v>
+        <v>6.1359</v>
       </c>
       <c r="M14" t="n">
         <v>-3.8825</v>
@@ -1546,13 +1546,13 @@
         <v>14.1379</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6849999999999997</v>
+        <v>1.0274</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7486</v>
+        <v>2.0909</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0635</v>
+        <v>-1.0636</v>
       </c>
       <c r="V14" t="n">
         <v>1.6743</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>12.0885</v>
+        <v>10.6807</v>
       </c>
       <c r="E15" t="n">
-        <v>11.2016</v>
+        <v>9.8605</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8869</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>4.682</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9938</v>
+        <v>1.5859</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4443</v>
+        <v>1.1032</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5495</v>
+        <v>0.4828</v>
       </c>
       <c r="V15" t="n">
         <v>2.4552</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. RIGOT</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1364</v>
+        <v>0.1113</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1337</v>
+        <v>0.4032</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0027</v>
+        <v>-0.2919</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0982</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.958</v>
+        <v>1.6182</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8598</v>
+        <v>-1.5379</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.024</v>
+        <v>1.8024</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5411</v>
+        <v>2.0685</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5172</v>
+        <v>-0.2661</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0742</v>
+        <v>-1.7222</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4169</v>
+        <v>-0.4504</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3426</v>
+        <v>-1.2718</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>2.8276</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3874</v>
+        <v>-0.0565</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7677</v>
+        <v>0.0156</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3803</v>
+        <v>-0.0721</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3698</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.7602</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9215</v>
+        <v>0.0214</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9769</v>
+        <v>1.6474</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8984</v>
+        <v>-1.626</v>
       </c>
       <c r="G17" t="n">
         <v>0.2366</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4404</v>
+        <v>-0.4975</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.822</v>
+        <v>-0.1514</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.3461</v>
       </c>
       <c r="V17" t="n">
         <v>0.9347</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>P. RIGOT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1784</v>
+        <v>-0.5663</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4909</v>
+        <v>-0.8722</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6875</v>
+        <v>0.3058</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08019999999999999</v>
+        <v>-0.0982</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6182</v>
+        <v>-0.958</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5379</v>
+        <v>0.8598</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8024</v>
+        <v>-0.024</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0685</v>
+        <v>-0.5411</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2661</v>
+        <v>0.5172</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7222</v>
+        <v>-0.0742</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4504</v>
+        <v>-0.4169</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2718</v>
+        <v>0.3426</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8276</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3461</v>
+        <v>0.6847</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8784</v>
+        <v>0.7619</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4677</v>
+        <v>-0.0772</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.3698</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2815</v>
+        <v>-1.1697</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.169</v>
+        <v>-0.0572</v>
       </c>
       <c r="F19" t="n">
         <v>-1.1125</v>
@@ -1936,10 +1936,10 @@
         <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3545</v>
+        <v>-0.2427</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U19" t="n">
         <v>-0.149</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.016</v>
+        <v>-1.5869</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8336</v>
+        <v>-3.6101</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8177</v>
+        <v>2.0232</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2354</v>
@@ -2014,13 +2014,13 @@
         <v>2.6101</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3032</v>
+        <v>0.1259</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4194</v>
+        <v>-0.1959</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1162</v>
+        <v>0.3217</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5109</v>
+        <v>-1.9302</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8455</v>
+        <v>-1.9515</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3346</v>
+        <v>0.0213</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2453</v>
@@ -2092,13 +2092,13 @@
         <v>3.2626</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2434</v>
+        <v>0.3374</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0154</v>
+        <v>-0.1214</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7721</v>
+        <v>0.4587</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9347</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.084</v>
+        <v>-3.4609</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.482</v>
+        <v>-4.4957</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6019</v>
+        <v>1.0348</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7227</v>
+        <v>-4.3505</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4653</v>
+        <v>-2.43</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2574</v>
+        <v>-1.9204</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7612</v>
+        <v>-3.3933</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1492</v>
+        <v>-1.9797</v>
       </c>
       <c r="L22" t="n">
-        <v>0.612</v>
+        <v>-1.4136</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4838</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.4504</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8694</v>
+        <v>-0.5068</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.8276</v>
+        <v>3.0451</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>3.0451</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4011</v>
+        <v>-0.286</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8242</v>
+        <v>-0.3629</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4231</v>
+        <v>0.0769</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9347</v>
+        <v>-1.8695</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X22" t="n">
         <v>-1.13</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4525</v>
+        <v>-4.2499</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9427</v>
+        <v>-2.602</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4902</v>
+        <v>-1.6479</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.3505</v>
+        <v>-3.1149</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.43</v>
+        <v>-1.6877</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9204</v>
+        <v>-1.4272</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.3933</v>
+        <v>-2.2271</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9797</v>
+        <v>-1.5203</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4136</v>
+        <v>-0.7068</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.8878</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4504</v>
+        <v>-0.1674</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5068</v>
+        <v>-0.7204</v>
       </c>
       <c r="P23" t="n">
-        <v>3.0451</v>
+        <v>0.87</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.0451</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2776</v>
+        <v>-0.8751</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8099</v>
+        <v>-0.3749</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4677</v>
+        <v>-0.5002</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8695</v>
+        <v>-1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-1.13</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8768</v>
+        <v>-4.4559</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.049</v>
+        <v>-1.8231</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8278</v>
+        <v>-2.6327</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1149</v>
+        <v>-0.7227</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6877</v>
+        <v>-0.4653</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4272</v>
+        <v>-0.2574</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2271</v>
+        <v>0.7612</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5203</v>
+        <v>0.1492</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7068</v>
+        <v>0.612</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8878</v>
+        <v>-1.4838</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1674</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7204</v>
+        <v>-0.8694</v>
       </c>
       <c r="P24" t="n">
-        <v>0.87</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R24" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.502</v>
+        <v>0.0291</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.822</v>
+        <v>0.4831</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.68</v>
+        <v>-0.4539</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.13</v>
+        <v>-0.9347</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X24" t="n">
         <v>-1.13</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.0967</v>
+        <v>-6.606400000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.500500000000001</v>
+        <v>-3.500699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.596</v>
+        <v>-3.105799999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.912700000000001</v>
+        <v>-7.912699999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4856000000000007</v>
+        <v>-0.4856000000000006</v>
       </c>
       <c r="I25" t="n">
         <v>-7.426799999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>3.882400000000001</v>
+        <v>3.8824</v>
       </c>
       <c r="K25" t="n">
         <v>5.1732</v>
@@ -2389,13 +2389,13 @@
         <v>-11.7948</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.6588</v>
+        <v>-5.658799999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-6.136</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1751</v>
+        <v>2.175100000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.1379</v>
@@ -2404,19 +2404,19 @@
         <v>16.313</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6849000000000005</v>
+        <v>0.8052000000000002</v>
       </c>
       <c r="T25" t="n">
         <v>1.0636</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7484</v>
+        <v>-0.2584</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.6742</v>
+        <v>-1.674199999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>5.6913</v>
+        <v>5.691299999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-7.3655</v>
